--- a/output_data/DC_Storage_OG.xlsx
+++ b/output_data/DC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1837.950754981417</v>
+        <v>10377.80127800189</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1815.443197727874</v>
+        <v>10355.36544910677</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1800.205117951154</v>
+        <v>10337.83948677191</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1782.898707611843</v>
+        <v>10307.76264503525</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1757.86443090745</v>
+        <v>10248.66678880805</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1749.787233221012</v>
+        <v>10200.71595454402</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1838.385974055199</v>
+        <v>10814.81571011446</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1940.198374989267</v>
+        <v>11461.2922118497</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2038.703202042253</v>
+        <v>12056.10844135384</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2153.128068968618</v>
+        <v>12793.41513763826</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2265.220075699324</v>
+        <v>13186.95354421193</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2449.458768143003</v>
+        <v>13866.06051430193</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2604.865577540533</v>
+        <v>14896.96003939866</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2912.036482180374</v>
+        <v>16191.1287484907</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3197.087225602809</v>
+        <v>17335.00350354526</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3323.728882315692</v>
+        <v>18087.41157813465</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3323.728882315692</v>
+        <v>18087.41157813465</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3226.408338052115</v>
+        <v>17308.64867999078</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2927.02784554866</v>
+        <v>15485.40415725773</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2553.855738441292</v>
+        <v>13401.26054390749</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>2224.308988195583</v>
+        <v>11451.89963058551</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1987.016958622052</v>
+        <v>9832.389164009173</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1827.304134426131</v>
+        <v>8617.282414209672</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1725.395129599798</v>
+        <v>7817.956994120972</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3731.721071073676</v>
+        <v>20841.43613350237</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_Storage_OG.xlsx
+++ b/output_data/DC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10377.80127800189</v>
+        <v>4452.782987182677</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10355.36544910677</v>
+        <v>4430.335571270341</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10337.83948677191</v>
+        <v>4414.933180419561</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10307.76264503525</v>
+        <v>4392.263808120009</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10248.66678880805</v>
+        <v>4358.21559227587</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10200.71595454402</v>
+        <v>4334.593289122196</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10814.81571011446</v>
+        <v>4576.041582742581</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11461.2922118497</v>
+        <v>4869.77723334231</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12056.10844135384</v>
+        <v>5110.721191052842</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12793.41513763826</v>
+        <v>5478.265643592903</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13186.95354421193</v>
+        <v>5753.508056649798</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13866.06051430193</v>
+        <v>6192.206424227634</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14896.96003939866</v>
+        <v>6723.616685011455</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16191.1287484907</v>
+        <v>7404.267054433322</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17335.00350354526</v>
+        <v>7885.069706195635</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18087.41157813465</v>
+        <v>8051.099860800744</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18087.41157813465</v>
+        <v>8045.619771108182</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17308.64867999078</v>
+        <v>7730.414353330752</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>15485.40415725773</v>
+        <v>6894.304299021535</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13401.26054390749</v>
+        <v>5997.687892826328</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>11451.89963058551</v>
+        <v>5138.495681778476</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>9832.389164009173</v>
+        <v>4452.011397514118</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>8617.282414209672</v>
+        <v>3960.282574947208</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>7817.956994120972</v>
+        <v>3608.121678228641</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20841.43613350237</v>
+        <v>8966.164061952075</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_Storage_OG.xlsx
+++ b/output_data/DC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4452.782987182677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4430.335571270341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4414.933180419561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4392.263808120009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4358.21559227587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4334.593289122196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4576.041582742581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4869.77723334231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5110.721191052842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5478.265643592903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5753.508056649798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6192.206424227634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6723.616685011455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7404.267054433322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7885.069706195635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8051.099860800744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8045.619771108182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7730.414353330752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6894.304299021535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>5997.687892826328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>5138.495681778476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>4452.011397514118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3960.282574947208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3608.121678228641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8966.164061952075</v>
+        <v>5979.200359509959</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/DC_Storage_OG.xlsx
+++ b/output_data/DC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2915.85650225984</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2893.409086347503</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2877.028917718946</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2855.648434308283</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2817.333551797478</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2764.32595201301</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3016.171374222589</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3326.776426232219</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3606.437131392708</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4061.940887052479</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4424.37549590715</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4907.472771419546</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5326.794280025241</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5326.794280025241</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5326.794280025241</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>5326.794280025241</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5326.794280025241</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4986.01003880985</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4394.144007695934</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3802.277976582019</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3210.411945468103</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2618.545914354188</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2084.531371159789</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1748.706976035957</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5979.200359509959</v>
+        <v>5918.660311139157</v>
       </c>
     </row>
   </sheetData>
